--- a/虎歌/最终评分结果.xlsx
+++ b/虎歌/最终评分结果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\best igl wiki\虎歌\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C93ECF-5F1C-4581-8EB3-7CDA1A23DC8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C9BBCC-31F7-45F8-A4AE-25C2CB7EC871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31087" yWindow="-109" windowWidth="31196" windowHeight="18974" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17195" yWindow="73" windowWidth="17038" windowHeight="17981" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,100 +52,116 @@
     <t>混的太逼真</t>
   </si>
   <si>
+    <t>访夜</t>
+  </si>
+  <si>
+    <t>大斧碎🀄️口</t>
+  </si>
+  <si>
+    <t>红中惹的祸</t>
+  </si>
+  <si>
+    <t>大约在第七</t>
+  </si>
+  <si>
+    <t>过虎</t>
+  </si>
+  <si>
+    <t>虎八分钱(PHONK)完整版</t>
+  </si>
+  <si>
+    <t>掉CC我不习惯</t>
+  </si>
+  <si>
+    <t>向白莲奔去</t>
+  </si>
+  <si>
+    <t>你快回来 指挥也能打伤害</t>
+  </si>
+  <si>
+    <t>一路向K</t>
+  </si>
+  <si>
+    <t>huge vs 卡神 危险派对</t>
+  </si>
+  <si>
+    <t>不是因为夺冠才少你，只是因为少你才夺冠</t>
+  </si>
+  <si>
+    <t>王虎我们的战绩好像跳楼机</t>
+  </si>
+  <si>
+    <t>念虎圣帝君</t>
+  </si>
+  <si>
+    <t>有点虎</t>
+  </si>
+  <si>
+    <t>DF地狱归来单曲《💩黏》</t>
+  </si>
+  <si>
+    <t>冠军转移</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>孤虎者</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>一挑五</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>红中红红中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>太明治</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>白莲花的葬礼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>夜访 延迟三毫秒</t>
-  </si>
-  <si>
-    <t>访夜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>虎哥虎哥在哪里</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>进击的巨大！日本小姑娘激情献唱《红中の子》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>虎阳假</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>话连错</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>阳光开朗三明治</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>群虎</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>讨厌线下梦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>突然的红中</t>
-  </si>
-  <si>
-    <t>大斧碎🀄️口</t>
-  </si>
-  <si>
-    <t>红中惹的祸</t>
-  </si>
-  <si>
-    <t>大约在第七</t>
-  </si>
-  <si>
-    <t>过虎</t>
-  </si>
-  <si>
-    <t>虎八分钱(PHONK)完整版</t>
-  </si>
-  <si>
-    <t>掉CC我不习惯</t>
-  </si>
-  <si>
-    <t>向白莲奔去</t>
-  </si>
-  <si>
-    <t>你快回来 指挥也能打伤害</t>
-  </si>
-  <si>
-    <t>一路向K</t>
-  </si>
-  <si>
-    <t>huge vs 卡神 危险派对</t>
-  </si>
-  <si>
-    <t>不是因为夺冠才少你，只是因为少你才夺冠</t>
-  </si>
-  <si>
-    <t>王虎我们的战绩好像跳楼机</t>
-  </si>
-  <si>
-    <t>念虎圣帝君</t>
-  </si>
-  <si>
-    <t>有点虎</t>
-  </si>
-  <si>
-    <t>DF地狱归来单曲《💩黏》</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>大笑江虎</t>
-  </si>
-  <si>
-    <t>阳光开朗三明治</t>
-  </si>
-  <si>
-    <t>虎哥虎哥在哪里</t>
-  </si>
-  <si>
-    <t>太明治</t>
-  </si>
-  <si>
-    <t>冠军转移</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -164,6 +180,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -627,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2">
         <v>41</v>
@@ -650,7 +667,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2">
         <v>41</v>
@@ -673,7 +690,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2">
         <v>41</v>
@@ -696,7 +713,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C8" s="2">
         <v>41</v>
@@ -719,7 +736,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2">
         <v>41</v>
@@ -742,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="2">
         <v>41</v>
@@ -765,7 +782,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C11" s="2">
         <v>41</v>
@@ -788,7 +805,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2">
         <v>41</v>
@@ -811,7 +828,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2">
         <v>41</v>
@@ -834,7 +851,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
         <v>41</v>
@@ -857,7 +874,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2">
         <v>41</v>
@@ -880,7 +897,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2">
         <v>41</v>
@@ -903,7 +920,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2">
         <v>41</v>
@@ -926,7 +943,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C18" s="2">
         <v>41</v>
@@ -949,7 +966,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C19" s="2">
         <v>41</v>
@@ -972,7 +989,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C20" s="2">
         <v>41</v>
@@ -995,7 +1012,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C21" s="2">
         <v>41</v>
@@ -1018,7 +1035,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2">
         <v>41</v>
@@ -1041,7 +1058,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C23" s="2">
         <v>41</v>
@@ -1064,7 +1081,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C24" s="2">
         <v>41</v>
@@ -1087,7 +1104,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C25" s="2">
         <v>41</v>
@@ -1110,7 +1127,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C26" s="2">
         <v>41</v>
@@ -1133,7 +1150,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C27" s="2">
         <v>41</v>
@@ -1156,7 +1173,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C28" s="2">
         <v>41</v>
@@ -1179,7 +1196,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C29" s="2">
         <v>41</v>
@@ -1202,7 +1219,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C30" s="2">
         <v>41</v>
@@ -1225,7 +1242,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C31" s="2">
         <v>41</v>
@@ -1248,7 +1265,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C32" s="2">
         <v>41</v>
@@ -1271,7 +1288,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C33" s="2">
         <v>41</v>
@@ -1294,7 +1311,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C34" s="2">
         <v>41</v>
@@ -1317,7 +1334,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C35" s="2">
         <v>41</v>
@@ -1340,7 +1357,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C36" s="2">
         <v>41</v>
